--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_68_R7.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_68_R7.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1041</v>
+        <v>12.7417</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1905</v>
+        <v>8.6937</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9135</v>
+        <v>4.048</v>
       </c>
       <c r="G2" t="n">
         <v>9.6539</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1581</v>
+        <v>0.4795</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8883</v>
+        <v>-0.3851</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7301</v>
+        <v>0.8646</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0424</v>
+        <v>4.0323</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9478</v>
+        <v>2.4878</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0945</v>
+        <v>1.5445</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0428</v>
+        <v>1.9065</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8726</v>
+        <v>-0.6399</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8298</v>
+        <v>2.5463</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2817</v>
+        <v>2.5001</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6336</v>
+        <v>0.1078</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3519</v>
+        <v>2.3923</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7611</v>
+        <v>-0.5937</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2391</v>
+        <v>-0.7477</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5221</v>
+        <v>0.154</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3037</v>
+        <v>1.0537</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0578</v>
+        <v>0.1654</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2459</v>
+        <v>0.8883</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7312</v>
+        <v>2.9553</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5338</v>
+        <v>1.1969</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1974</v>
+        <v>1.7585</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7243</v>
+        <v>1.0428</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8581</v>
+        <v>1.8726</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1338</v>
+        <v>-0.8298</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3287</v>
+        <v>0.2817</v>
       </c>
       <c r="K4" t="n">
-        <v>2.931</v>
+        <v>1.6336</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-1.3519</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6044</v>
+        <v>0.7611</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.073</v>
+        <v>0.2391</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4685</v>
+        <v>0.5221</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="R4" t="n">
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6332</v>
+        <v>1.2166</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9911</v>
+        <v>0.3068</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6421</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3943</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7053</v>
+        <v>2.4425</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2952</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4101</v>
+        <v>1.6597</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9065</v>
+        <v>1.7243</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6399</v>
+        <v>1.8581</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5463</v>
+        <v>-0.1338</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5001</v>
+        <v>2.3287</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1078</v>
+        <v>2.931</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3923</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5937</v>
+        <v>-0.6044</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7477</v>
+        <v>-1.073</v>
       </c>
       <c r="O5" t="n">
-        <v>0.154</v>
+        <v>0.4685</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7266</v>
+        <v>1.3445</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0272</v>
+        <v>0.2401</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7538</v>
+        <v>1.1044</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>-0.3943</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>D. SIRVYDIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9301</v>
+        <v>1.9014</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9252</v>
+        <v>-1.0965</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8553</v>
+        <v>2.9979</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2985</v>
+        <v>1.4513</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9496</v>
+        <v>-0.1379</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2481</v>
+        <v>1.5893</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6272</v>
+        <v>1.1441</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4068</v>
+        <v>-0.0301</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.0341</v>
+        <v>1.1742</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3288</v>
+        <v>0.3072</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5427999999999999</v>
+        <v>-0.1078</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.214</v>
+        <v>0.415</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.6237</v>
+        <v>-1.8556</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1564</v>
+        <v>0.2181</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8883</v>
+        <v>-0.3851</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0447</v>
+        <v>0.6032</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SIRVYDIS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9277</v>
+        <v>1.729</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5998</v>
+        <v>-1.2607</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5274</v>
+        <v>2.9897</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4513</v>
+        <v>-0.2985</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1379</v>
+        <v>0.9496</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5893</v>
+        <v>-1.2481</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1441</v>
+        <v>-0.6272</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0301</v>
+        <v>0.4068</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1742</v>
+        <v>-1.0341</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3072</v>
+        <v>0.3288</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1078</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0.415</v>
+        <v>-0.214</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8556</v>
+        <v>-1.6237</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7556</v>
+        <v>0.9553</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8883</v>
+        <v>-0.2238</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1327</v>
+        <v>1.1791</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6528</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0958</v>
+        <v>-0.5676</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7543</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9432</v>
+        <v>0.3705</v>
       </c>
       <c r="T8" t="n">
-        <v>0.637</v>
+        <v>0.1652</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3062</v>
+        <v>0.2054</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. RUBSTAVICIUS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5284</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2799</v>
+        <v>0.6866</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8083</v>
+        <v>-0.7862</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1495</v>
+        <v>0.0146</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2905</v>
+        <v>-1.0863</v>
       </c>
       <c r="I9" t="n">
-        <v>1.141</v>
+        <v>1.1009</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3546</v>
+        <v>0.0506</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7863</v>
+        <v>-0.6855</v>
       </c>
       <c r="L9" t="n">
-        <v>1.141</v>
+        <v>0.7361</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5041</v>
+        <v>-0.036</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5041</v>
+        <v>-0.4008</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.3648</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0747</v>
+        <v>0.4039</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0747</v>
+        <v>-0.2043</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.6082</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5361</v>
+        <v>-1.214</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5361</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>M. RUBSTAVICIUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6454</v>
+        <v>-0.5284</v>
       </c>
       <c r="E10" t="n">
-        <v>0.376</v>
+        <v>0.2799</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0214</v>
+        <v>-0.8083</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0146</v>
+        <v>-0.1495</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0863</v>
+        <v>-1.2905</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1009</v>
+        <v>1.141</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0506</v>
+        <v>0.3546</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6855</v>
+        <v>-0.7863</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7361</v>
+        <v>1.141</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.036</v>
+        <v>-0.5041</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4008</v>
+        <v>-0.5041</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3648</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1419</v>
+        <v>-0.0747</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5149</v>
+        <v>-0.0747</v>
       </c>
       <c r="U10" t="n">
-        <v>0.373</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.214</v>
+        <v>-0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.2862</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0525</v>
+        <v>-0.7076</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7296</v>
+        <v>-2.1831</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6771</v>
+        <v>1.4755</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2861</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0738</v>
+        <v>0.4187</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8883</v>
+        <v>-0.3418</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9621</v>
+        <v>0.7604</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3677</v>
+        <v>-5.3005</v>
       </c>
       <c r="E12" t="n">
         <v>-6.2644</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.9639</v>
       </c>
       <c r="G12" t="n">
         <v>-2.637</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2125</v>
+        <v>1.2797</v>
       </c>
       <c r="T12" t="n">
         <v>0.3462</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8663</v>
+        <v>0.9335</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.4996</v>
+        <v>19.2463</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0084</v>
+        <v>2.755400000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>16.4908</v>
+        <v>16.4909</v>
       </c>
       <c r="G13" t="n">
         <v>11.668</v>
@@ -1450,7 +1450,7 @@
         <v>6.607200000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>0.05099999999999971</v>
+        <v>0.05099999999999993</v>
       </c>
       <c r="N13" t="n">
         <v>-2.543</v>
@@ -1468,13 +1468,13 @@
         <v>13.9173</v>
       </c>
       <c r="S13" t="n">
-        <v>6.9191</v>
+        <v>7.6658</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1379</v>
+        <v>-0.3910999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>8.056900000000001</v>
+        <v>8.056899999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.3196</v>
+        <v>6.7812</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8407</v>
+        <v>4.6048</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4789</v>
+        <v>2.1765</v>
       </c>
       <c r="G14" t="n">
         <v>2.2817</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1797</v>
+        <v>-0.3587</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4007</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5803</v>
+        <v>0.2779</v>
       </c>
       <c r="V14" t="n">
         <v>2.5387</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5502</v>
+        <v>1.8083</v>
       </c>
       <c r="E15" t="n">
         <v>1.7331</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.183</v>
+        <v>0.0751</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5738</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4818</v>
+        <v>-1.2237</v>
       </c>
       <c r="T15" t="n">
         <v>-1.3443</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1375</v>
+        <v>0.1206</v>
       </c>
       <c r="V15" t="n">
         <v>1.7501</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0126</v>
+        <v>0.4052</v>
       </c>
       <c r="E16" t="n">
         <v>0.3747</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3621</v>
+        <v>0.0304</v>
       </c>
       <c r="G16" t="n">
         <v>0.4457</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9871</v>
+        <v>-0.5946</v>
       </c>
       <c r="T16" t="n">
         <v>-0.5895</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3976</v>
+        <v>-0.005</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1418</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3301</v>
+        <v>0.2553</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2566</v>
+        <v>-1.0389</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.07340000000000001</v>
+        <v>1.2942</v>
       </c>
       <c r="G17" t="n">
-        <v>0.634</v>
+        <v>-0.1064</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0191</v>
+        <v>0.4021</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3851</v>
+        <v>-0.5085</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6704</v>
+        <v>0.8872</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6336</v>
+        <v>0.8136</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0368</v>
+        <v>0.0736</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0364</v>
+        <v>-0.9937</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3856</v>
+        <v>-0.4116</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.422</v>
+        <v>-0.5821</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7863</v>
+        <v>-0.3341</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8215</v>
+        <v>-0.7664</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0351</v>
+        <v>0.4323</v>
       </c>
       <c r="V17" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5475</v>
+        <v>-0.0155</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3927</v>
+        <v>-0.2566</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.2411</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1064</v>
+        <v>0.634</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4021</v>
+        <v>2.0191</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5085</v>
+        <v>-1.3851</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8872</v>
+        <v>1.6704</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8136</v>
+        <v>1.6336</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0736</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9937</v>
+        <v>-1.0364</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4116</v>
+        <v>0.3856</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5821</v>
+        <v>-1.422</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1369</v>
+        <v>-0.4718</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1202</v>
+        <v>-0.8215</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0167</v>
+        <v>0.3497</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9075</v>
+        <v>-1.0083</v>
       </c>
       <c r="E19" t="n">
         <v>-0.2987</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6087</v>
+        <v>-0.7096</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9149</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0075</v>
+        <v>-0.0934</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3062</v>
+        <v>0.2054</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2177</v>
+        <v>-1.6057</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1946</v>
+        <v>-0.8407</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0231</v>
+        <v>-0.765</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3108</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6207</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6642</v>
+        <v>-0.3104</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0435</v>
+        <v>0.3016</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7501</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0032</v>
+        <v>-2.7115</v>
       </c>
       <c r="E21" t="n">
         <v>-2.4726</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5306</v>
+        <v>-0.2389</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4822</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2195</v>
+        <v>-0.9278</v>
       </c>
       <c r="T21" t="n">
         <v>-0.9709</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2486</v>
+        <v>0.0431</v>
       </c>
       <c r="V21" t="n">
         <v>0.3943</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3345</v>
+        <v>-4.3681</v>
       </c>
       <c r="E22" t="n">
         <v>-4.3243</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0103</v>
+        <v>-0.0439</v>
       </c>
       <c r="G22" t="n">
         <v>-2.472</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.329</v>
+        <v>-0.3626</v>
       </c>
       <c r="T22" t="n">
         <v>-0.5228</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1937</v>
+        <v>0.1601</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7879</v>
+        <v>-5.994</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9355</v>
+        <v>-4.7612</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8524</v>
+        <v>-1.2328</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3387</v>
@@ -2248,13 +2248,13 @@
         <v>3.0154</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8602</v>
+        <v>-0.3459</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2118</v>
+        <v>-1.0374</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0719</v>
+        <v>0.6915</v>
       </c>
       <c r="V23" t="n">
         <v>-4.0052</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-11.2536</v>
+        <v>-10.4736</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.564399999999999</v>
+        <v>-9.210599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6892</v>
+        <v>-1.2631</v>
       </c>
       <c r="G24" t="n">
         <v>-6.8308</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4049</v>
+        <v>-0.6249</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1123</v>
+        <v>-0.7585</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2926</v>
+        <v>0.1336</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9304</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-18.4996</v>
+        <v>-16.9267</v>
       </c>
       <c r="E25" t="n">
-        <v>-16.4909</v>
+        <v>-16.491</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0086</v>
+        <v>-0.4359999999999995</v>
       </c>
       <c r="G25" t="n">
         <v>-11.6682</v>
@@ -2377,7 +2377,7 @@
         <v>-9.2011</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.05099999999999927</v>
+        <v>-0.05100000000000016</v>
       </c>
       <c r="K25" t="n">
         <v>2.543</v>
@@ -2392,10 +2392,10 @@
         <v>-5.0097</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.607399999999999</v>
+        <v>-6.6074</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1598</v>
+        <v>1.159800000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.9172</v>
@@ -2404,13 +2404,13 @@
         <v>15.0769</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.918799999999999</v>
+        <v>-5.3463</v>
       </c>
       <c r="T25" t="n">
-        <v>-8.056900000000001</v>
+        <v>-8.057</v>
       </c>
       <c r="U25" t="n">
-        <v>1.1377</v>
+        <v>2.7108</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
